--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4469,6 +4469,243 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124893729</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98018</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>617665</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6659969</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Carolina Jonsell</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Carolina Jonsell, Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124893803</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80763</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pålsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>617564</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6659922</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Carolina Jonsell</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Carolina Jonsell, Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -4471,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893729</v>
+        <v>124893803</v>
       </c>
       <c r="B35" t="n">
-        <v>98018</v>
+        <v>80763</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,31 +4483,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4515,10 +4518,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617665</v>
+        <v>617564</v>
       </c>
       <c r="R35" t="n">
-        <v>6659969</v>
+        <v>6659922</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4588,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124893803</v>
+        <v>124893729</v>
       </c>
       <c r="B36" t="n">
-        <v>80763</v>
+        <v>98018</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4600,34 +4603,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617564</v>
+        <v>617665</v>
       </c>
       <c r="R36" t="n">
-        <v>6659922</v>
+        <v>6659969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -4471,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893803</v>
+        <v>124893729</v>
       </c>
       <c r="B35" t="n">
-        <v>80763</v>
+        <v>98018</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,34 +4483,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4518,10 +4515,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617564</v>
+        <v>617665</v>
       </c>
       <c r="R35" t="n">
-        <v>6659922</v>
+        <v>6659969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4591,10 +4588,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124893729</v>
+        <v>124893803</v>
       </c>
       <c r="B36" t="n">
-        <v>98018</v>
+        <v>80763</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4603,31 +4600,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617665</v>
+        <v>617564</v>
       </c>
       <c r="R36" t="n">
-        <v>6659969</v>
+        <v>6659922</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carolina Jonsell, Elvira Klang</t>
+          <t>Elvira Klang, Carolina Jonsell</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -4471,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893729</v>
+        <v>124893803</v>
       </c>
       <c r="B35" t="n">
-        <v>98018</v>
+        <v>80900</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,31 +4483,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4515,10 +4518,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617665</v>
+        <v>617564</v>
       </c>
       <c r="R35" t="n">
-        <v>6659969</v>
+        <v>6659922</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4588,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124893803</v>
+        <v>124893729</v>
       </c>
       <c r="B36" t="n">
-        <v>80763</v>
+        <v>98186</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4600,34 +4603,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617564</v>
+        <v>617665</v>
       </c>
       <c r="R36" t="n">
-        <v>6659922</v>
+        <v>6659969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elvira Klang, Carolina Jonsell</t>
+          <t>Carolina Jonsell, Elvira Klang</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -4471,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893803</v>
+        <v>124893729</v>
       </c>
       <c r="B35" t="n">
-        <v>80900</v>
+        <v>98186</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,34 +4483,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4518,10 +4515,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617564</v>
+        <v>617665</v>
       </c>
       <c r="R35" t="n">
-        <v>6659922</v>
+        <v>6659969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4591,10 +4588,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124893729</v>
+        <v>124893803</v>
       </c>
       <c r="B36" t="n">
-        <v>98186</v>
+        <v>80900</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4603,31 +4600,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617665</v>
+        <v>617564</v>
       </c>
       <c r="R36" t="n">
-        <v>6659969</v>
+        <v>6659922</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 49503-2023 artfynd.xlsx
+++ b/artfynd/A 49503-2023 artfynd.xlsx
@@ -4471,43 +4471,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124893729</v>
+        <v>124893803</v>
       </c>
       <c r="B35" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4515,10 +4513,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617665</v>
+        <v>617564</v>
       </c>
       <c r="R35" t="n">
-        <v>6659969</v>
+        <v>6659922</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4588,46 +4586,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124893803</v>
+        <v>124893729</v>
       </c>
       <c r="B36" t="n">
-        <v>80900</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4635,10 +4625,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617564</v>
+        <v>617665</v>
       </c>
       <c r="R36" t="n">
-        <v>6659922</v>
+        <v>6659969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
